--- a/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,9</t>
+          <t>-0,06; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,19</t>
+          <t>-1,44; 1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,73</t>
+          <t>0,24; 3,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,55</t>
+          <t>0,14; 2,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,17</t>
+          <t>-0,4; 2,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,63</t>
+          <t>1,17; 3,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,32</t>
+          <t>0,45; 2,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,32</t>
+          <t>-0,44; 1,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,19</t>
+          <t>1,13; 3,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 207,09</t>
+          <t>-7,69; 211,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 84,84</t>
+          <t>-57,94; 86,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 250,67</t>
+          <t>5,42; 265,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 236,93</t>
+          <t>1,55; 231,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 178,67</t>
+          <t>-25,19; 181,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,46; 332,66</t>
+          <t>54,96; 340,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 167,91</t>
+          <t>18,46; 157,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 91,69</t>
+          <t>-21,12; 92,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,33; 220,37</t>
+          <t>51,85; 225,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,39</t>
+          <t>0,12; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,85</t>
+          <t>-0,35; 0,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,97</t>
+          <t>0,48; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,13; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,46</t>
+          <t>0,04; 1,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 35,27</t>
+          <t>1,71; 33,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,29</t>
+          <t>0,35; 1,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,97</t>
+          <t>0,06; 0,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 22,25</t>
+          <t>1,29; 20,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 515,22</t>
+          <t>3,45; 563,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 346,88</t>
+          <t>-43,81; 317,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 770,98</t>
+          <t>51,96; 723,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 339,28</t>
+          <t>4,72; 390,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 361,7</t>
+          <t>-3,33; 392,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>215,3; 8643,17</t>
+          <t>210,07; 10371,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 315,77</t>
+          <t>37,59; 300,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 236,25</t>
+          <t>3,07; 221,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209,63; 6164,07</t>
+          <t>201,02; 5135,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,03</t>
+          <t>0,27; 3,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,93</t>
+          <t>-0,33; 0,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,87</t>
+          <t>1,02; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,01</t>
+          <t>-1,61; 1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,62</t>
+          <t>-2,25; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,33</t>
+          <t>-1,02; 2,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,77</t>
+          <t>-0,34; 1,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,49</t>
+          <t>-0,86; 0,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,48</t>
+          <t>0,51; 2,64</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,68; 306,62</t>
+          <t>-69,48; 278,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,45; 98,12</t>
+          <t>-85,71; 111,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 320,73</t>
+          <t>-48,15; 318,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 449,04</t>
+          <t>-40,55; 348,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,26; 140,86</t>
+          <t>-74,52; 141,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,08; 527,04</t>
+          <t>20,69; 559,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,58</t>
+          <t>0,34; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,5</t>
+          <t>-0,5; 0,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,88</t>
+          <t>0,52; 1,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,58</t>
+          <t>0,32; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,04</t>
+          <t>-0,11; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 24,28</t>
+          <t>1,52; 24,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,4</t>
+          <t>0,49; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,63</t>
+          <t>-0,12; 0,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 14,46</t>
+          <t>1,24; 14,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,19; 223,65</t>
+          <t>27,69; 234,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 77,51</t>
+          <t>-42,56; 65,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,17; 262,56</t>
+          <t>38,19; 266,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,66; 172,92</t>
+          <t>21,1; 161,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 113,59</t>
+          <t>-8,28; 112,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>110,96; 2094,15</t>
+          <t>115,47; 2564,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,24; 160,76</t>
+          <t>40,98; 158,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 71,87</t>
+          <t>-10,58; 75,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>114,1; 1524,99</t>
+          <t>113,38; 1529,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,92</t>
+          <t>-0,01; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,23</t>
+          <t>-1,35; 1,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,74</t>
+          <t>0,35; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,56</t>
+          <t>0,22; 2,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,0</t>
+          <t>-0,39; 2,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,65</t>
+          <t>1,19; 3,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,31</t>
+          <t>0,4; 2,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,3</t>
+          <t>-0,47; 1,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,23</t>
+          <t>1,09; 3,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>145,79%</t>
+          <t>146,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121,08%</t>
+          <t>123,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 211,91</t>
+          <t>-4,94; 236,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 86,43</t>
+          <t>-53,69; 99,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 265,05</t>
+          <t>10,74; 272,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 231,05</t>
+          <t>10,58; 232,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 181,02</t>
+          <t>-23,51; 176,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,96; 340,19</t>
+          <t>52,08; 323,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 157,55</t>
+          <t>13,3; 153,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 92,13</t>
+          <t>-22,98; 90,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,85; 225,25</t>
+          <t>48,3; 226,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,84</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,42</t>
+          <t>0,09; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,77</t>
+          <t>-0,27; 0,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,08</t>
+          <t>0,69; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,57</t>
+          <t>0,22; 1,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,46</t>
+          <t>0,06; 1,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 33,32</t>
+          <t>1,46; 3,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,28</t>
+          <t>0,31; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,94</t>
+          <t>0,08; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 20,66</t>
+          <t>1,24; 2,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237,18%</t>
+          <t>277,15%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1566,25%</t>
+          <t>324,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1001,05%</t>
+          <t>305,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 563,92</t>
+          <t>-3,42; 551,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 317,62</t>
+          <t>-40,07; 353,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,96; 723,6</t>
+          <t>52,97; 969,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 390,3</t>
+          <t>17,65; 370,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 392,74</t>
+          <t>1,41; 428,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>210,07; 10371,4</t>
+          <t>127,14; 739,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,59; 300,25</t>
+          <t>30,1; 308,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 221,43</t>
+          <t>5,0; 238,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201,02; 5135,84</t>
+          <t>145,86; 648,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,05</t>
+          <t>0,1; 2,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,91</t>
+          <t>-0,32; 0,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,9</t>
+          <t>1,04; 3,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,95</t>
+          <t>-1,59; 2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,65</t>
+          <t>-2,13; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,38</t>
+          <t>-0,9; 2,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,78</t>
+          <t>-0,23; 1,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,56</t>
+          <t>-0,91; 0,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,64</t>
+          <t>0,47; 2,4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1232,27%</t>
+          <t>1261,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>177,83%</t>
+          <t>177,73%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 278,78</t>
+          <t>-70,98; 262,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,71; 111,01</t>
+          <t>-87,85; 118,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 318,72</t>
+          <t>-39,37; 236,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 348,67</t>
+          <t>-32,23; 438,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 141,97</t>
+          <t>-78,36; 145,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,69; 559,55</t>
+          <t>29,28; 603,77</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,65</t>
+          <t>0,3; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,46</t>
+          <t>-0,49; 0,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,87</t>
+          <t>0,75; 2,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,51</t>
+          <t>0,4; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,07</t>
+          <t>-0,13; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 24,33</t>
+          <t>1,24; 2,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,34</t>
+          <t>0,52; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,63</t>
+          <t>-0,14; 0,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 14,62</t>
+          <t>1,19; 2,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132,94%</t>
+          <t>153,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>609,88%</t>
+          <t>158,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>408,81%</t>
+          <t>157,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,69; 234,03</t>
+          <t>21,31; 228,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 65,42</t>
+          <t>-40,16; 72,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,19; 266,29</t>
+          <t>60,33; 298,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,1; 161,66</t>
+          <t>25,75; 174,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 112,12</t>
+          <t>-9,32; 120,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>115,47; 2564,7</t>
+          <t>83,99; 280,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,98; 158,2</t>
+          <t>40,66; 160,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 75,87</t>
+          <t>-11,45; 75,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>113,38; 1529,5</t>
+          <t>94,69; 240,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
